--- a/FieryLedLamp/Таблица эффектов.xlsx
+++ b/FieryLedLamp/Таблица эффектов.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7744810F-ECBE-4B96-B6E7-2F8C2C719C57}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69A2044-2CE2-4512-AD1F-F07CC9ED13B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" tabRatio="168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8485,7 +8485,7 @@
         <v>10</v>
       </c>
       <c r="I55" s="38">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="J55" s="38">
         <v>35</v>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="Z55" s="2" t="str">
         <f t="shared" ca="1" si="94"/>
-        <v>49;10;140;35;Марио</v>
+        <v>49;10;65;35;Марио</v>
       </c>
       <c r="AA55" s="2" t="str">
         <f t="shared" ca="1" si="95"/>
